--- a/00-TrainRnns/tau-12/Theta/BestModels-1l.xlsx
+++ b/00-TrainRnns/tau-12/Theta/BestModels-1l.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,164 +507,164 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>195</v>
+        <v>919</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>model_arch7_r0.9_Ld0.3_Lp0.7_seed4556</t>
+          <t>model_arch31_r0.9_Ld0.3_Lp0.7_seed1628</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[7]</t>
+          <t>[31]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8476612218427995</v>
+        <v>0.4303336156015583</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9546230834654823</v>
+        <v>0.4062275204693908</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.71400548772692</v>
+        <v>-0.2250406683604296</v>
       </c>
       <c r="G2" t="n">
-        <v>-10.10390544112336</v>
+        <v>-8.17158682509873</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.817522602989239</v>
+        <v>-5.295830705458565</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.989746161997061</v>
+        <v>-0.4017710762622111</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.702921455466905</v>
+        <v>-0.3798650334747729</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5692520426244112</v>
+        <v>-0.1418997502782977</v>
       </c>
       <c r="L2" t="n">
-        <v>-7.329788122141146</v>
+        <v>-1.888779120190834</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8476612218427995</v>
+        <v>0.4303336156015583</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9546230834654823</v>
+        <v>0.4062275204693908</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.869805318402888</v>
+        <v>-2.357824739874835</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.15409708847335</v>
+        <v>-0.8016790058777674</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>919</v>
+        <v>1396</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_arch31_r0.9_Ld0.3_Lp0.7_seed1628</t>
+          <t>model_arch47_r0.9_Ld0.3_Lp0.7_seed6942</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[31]</t>
+          <t>[47]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4303336156015583</v>
+        <v>0.4126937939020383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4062275204693908</v>
+        <v>0.5879042281840314</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2250406683604296</v>
+        <v>-2.70632298875574</v>
       </c>
       <c r="G3" t="n">
-        <v>-8.17158682509873</v>
+        <v>-9.888234479364305</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.295830705458565</v>
+        <v>-2.847838138378099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4017710762622111</v>
+        <v>-0.6001982171262925</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3798650334747729</v>
+        <v>-0.7358294216712735</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1418997502782977</v>
+        <v>0.0389677887447657</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.888779120190834</v>
+        <v>-5.326177115587102</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4303336156015583</v>
+        <v>0.4126937939020383</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4062275204693908</v>
+        <v>0.5879042281840314</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.357824739874835</v>
+        <v>-3.152233224591149</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2008200361815889</v>
+        <v>-1.05226559175417</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1457</v>
+        <v>2805</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch49_r0.9_Ld0.3_Lp0.7_seed7320</t>
+          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed4556</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[49]</t>
+          <t>[94]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.632214592981049</v>
+        <v>0.3947056154745049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5431827365529864</v>
+        <v>0.6389532286252977</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.731281061418865</v>
+        <v>-4.077517485788725</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.73011103257953</v>
+        <v>-8.640620672644907</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.040180667516656</v>
+        <v>-1.785885889875717</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.340440476576374</v>
+        <v>-0.418885740721413</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3215305528211017</v>
+        <v>-0.5555076743956637</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1997964274650252</v>
+        <v>-0.05958424139017704</v>
       </c>
       <c r="L4" t="n">
-        <v>-6.123364462235147</v>
+        <v>-7.115977097090022</v>
       </c>
       <c r="M4" t="n">
-        <v>0.632214592981049</v>
+        <v>0.3947056154745049</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5431827365529864</v>
+        <v>0.6389532286252977</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.441015975097521</v>
+        <v>-3.236282685986661</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2508393474913829</v>
+        <v>-1.07006236640486</v>
       </c>
     </row>
     <row r="5">
@@ -718,331 +718,61 @@
         <v>-3.408986375570983</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2511806363966358</v>
+        <v>-1.11570493589753</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>2232</v>
+        <v>1457</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch75_r0.01_Ld0.3_Lp0.7_seed7320</t>
+          <t>model_arch49_r0.9_Ld0.3_Lp0.7_seed7320</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[75]</t>
+          <t>[49]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6320233443368044</v>
+        <v>0.632214592981049</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6517243488606096</v>
+        <v>0.5431827365529864</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.280864641818686</v>
+        <v>-2.731281061418865</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.559782849973486</v>
+        <v>-10.73011103257953</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.337276066354437</v>
+        <v>-3.040180667516656</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.043746639581934</v>
+        <v>-1.340440476576374</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2190339750818646</v>
+        <v>-0.3215305528211017</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3237175657124614</v>
+        <v>0.1997964274650252</v>
       </c>
       <c r="L6" t="n">
-        <v>-9.064848598937775</v>
+        <v>-6.123364462235147</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6320233443368044</v>
+        <v>0.632214592981049</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6517243488606096</v>
+        <v>0.5431827365529864</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.597405029433674</v>
+        <v>-3.441015975097521</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.252879764661844</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>2805</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>model_arch94_r0.9_Ld0.3_Lp0.7_seed4556</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[94]</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.3947056154745049</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.6389532286252977</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-4.077517485788725</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-8.640620672644907</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.785885889875717</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.418885740721413</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.5555076743956637</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.05958424139017704</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-7.115977097090022</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.3947056154745049</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.6389532286252977</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-3.236282685986661</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.2533612295409415</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>1396</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>model_arch47_r0.9_Ld0.3_Lp0.7_seed6942</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[47]</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4126937939020383</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.5879042281840314</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-2.70632298875574</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-9.888234479364305</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-2.847838138378099</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.6001982171262925</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.7358294216712735</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.0389677887447657</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-5.326177115587102</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.4126937939020383</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5879042281840314</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-3.152233224591149</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.2572100885521812</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>2924</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>model_arch98_r0.01_Ld0.3_Lp0.7_seed1628</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[98]</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.4003984111511641</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8517727228105412</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-4.072160818146213</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-9.203381597970344</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-1.401700942504661</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.5227132461932611</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.846895418142714</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.1457544114715408</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-9.459187226311988</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.4003984111511641</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.8517727228105412</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-3.664541951534389</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.2663259811450748</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>2299</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>model_arch77_r0.9_Ld0.3_Lp0.7_seed1628</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[77]</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.6884495042897252</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.6109376871497142</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-5.142789930602711</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-9.046123518005553</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.8725553387710689</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.2488806007452</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.0217365676838932</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.5033107643303104</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-9.835064760428478</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.6884495042897252</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.6109376871497142</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-3.66626285027237</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.2688795373586704</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>2803</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>model_arch94_r0.01_Ld0.3_Lp0.7_seed1896</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[94]</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.4140297626146024</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.676113670089957</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-3.572958406070743</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-9.789153240653217</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.984481733032841</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.7015610428315413</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-0.566545681447163</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.07410079000441727</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-7.290741748827749</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.4140297626146024</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.676113670089957</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-3.425648948981096</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.2754926080446342</v>
+        <v>-1.124550834831195</v>
       </c>
     </row>
   </sheetData>
